--- a/artfynd/A 13483-2022 artfynd.xlsx
+++ b/artfynd/A 13483-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13483-2022 artfynd.xlsx
+++ b/artfynd/A 13483-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -908,7 +908,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102897594</v>
+        <v>104025368</v>
       </c>
       <c r="B4" t="n">
         <v>78569</v>
@@ -944,17 +944,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storberget, Jmt</t>
+          <t>Storberget-Storbergetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564403.8271050876</v>
+        <v>564404.7290194675</v>
       </c>
       <c r="R4" t="n">
-        <v>7014799.756553903</v>
+        <v>7014799.77459014</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,22 +978,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,25 +1007,29 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102897580</v>
+        <v>104025327</v>
       </c>
       <c r="B5" t="n">
         <v>96334</v>
@@ -1061,17 +1065,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storberget, Jmt</t>
+          <t>Storberget-Storbergetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564457.4121051542</v>
+        <v>564457.3940783725</v>
       </c>
       <c r="R5" t="n">
-        <v>7014985.087173179</v>
+        <v>7014985.987806616</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,22 +1099,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,15 +1129,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1370,7 +1378,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102897593</v>
+        <v>104025371</v>
       </c>
       <c r="B8" t="n">
         <v>77259</v>
@@ -1406,17 +1414,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Storberget, Jmt</t>
+          <t>Storberget-Storbergetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564350.8221512076</v>
+        <v>564350.8041544867</v>
       </c>
       <c r="R8" t="n">
-        <v>7014810.861103606</v>
+        <v>7014811.761785488</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,22 +1448,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,15 +1478,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1715,7 +1727,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>102897583</v>
+        <v>104025366</v>
       </c>
       <c r="B11" t="n">
         <v>78596</v>
@@ -1751,17 +1763,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Storberget, Jmt</t>
+          <t>Storberget-Storbergetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564386.6014841492</v>
+        <v>564386.5834773997</v>
       </c>
       <c r="R11" t="n">
-        <v>7014826.443373461</v>
+        <v>7014827.344051048</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1785,22 +1797,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,21 +1826,25 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1948,7 +1964,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>102897578</v>
+        <v>104025279</v>
       </c>
       <c r="B13" t="n">
         <v>78569</v>
@@ -1984,17 +2000,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Storberget, Jmt</t>
+          <t>Storberget-Storbergetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564468.874516179</v>
+        <v>564469.776387642</v>
       </c>
       <c r="R13" t="n">
-        <v>7014953.331159774</v>
+        <v>7014953.349214448</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2018,22 +2034,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2047,25 +2063,29 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>sälglåga</t>
+          <t>Sälglåga</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>102897584</v>
+        <v>104025370</v>
       </c>
       <c r="B14" t="n">
         <v>78569</v>
@@ -2101,17 +2121,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Storberget, Jmt</t>
+          <t>Storberget-Storbergetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564373.5319573598</v>
+        <v>564373.5139542988</v>
       </c>
       <c r="R14" t="n">
-        <v>7014803.205567234</v>
+        <v>7014804.106251282</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2135,22 +2155,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,25 +2184,29 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>102897592</v>
+        <v>104025369</v>
       </c>
       <c r="B15" t="n">
         <v>96334</v>
@@ -2218,17 +2242,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Storberget, Jmt</t>
+          <t>Storberget-Storbergetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>564388.6746326601</v>
+        <v>564388.6566253824</v>
       </c>
       <c r="R15" t="n">
-        <v>7014790.443111513</v>
+        <v>7014791.343799144</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2252,22 +2276,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2282,19 +2306,23 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>102897579</v>
+        <v>104025341</v>
       </c>
       <c r="B16" t="n">
         <v>96334</v>
@@ -2330,17 +2358,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Storberget, Jmt</t>
+          <t>Storberget-Storbergetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564454.0296880691</v>
+        <v>564454.0116622819</v>
       </c>
       <c r="R16" t="n">
-        <v>7014951.232008628</v>
+        <v>7014952.1326515</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2364,22 +2392,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2394,15 +2422,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2643,10 +2675,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>104025358</v>
+        <v>104025353</v>
       </c>
       <c r="B19" t="n">
-        <v>78569</v>
+        <v>96334</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2655,25 +2687,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2683,10 +2715,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>564357.6634856508</v>
+        <v>564358.7004139413</v>
       </c>
       <c r="R19" t="n">
-        <v>7014716.837585099</v>
+        <v>7014710.100289446</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2739,11 +2771,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2764,7 +2791,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>102897603</v>
+        <v>104025358</v>
       </c>
       <c r="B20" t="n">
         <v>78569</v>
@@ -2800,17 +2827,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Storberget, Jmt</t>
+          <t>Storberget-Storbergetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>564387.9774293588</v>
+        <v>564357.6634856508</v>
       </c>
       <c r="R20" t="n">
-        <v>7014712.487601109</v>
+        <v>7014716.837585099</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2834,22 +2861,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2863,28 +2890,32 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>102897605</v>
+        <v>104025356</v>
       </c>
       <c r="B21" t="n">
-        <v>90653</v>
+        <v>78569</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2893,41 +2924,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Storberget, Jmt</t>
+          <t>Storberget-Storbergetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>564405.5839172391</v>
+        <v>564388.8793681564</v>
       </c>
       <c r="R21" t="n">
-        <v>7014734.465236372</v>
+        <v>7014712.505632785</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2951,22 +2982,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2977,26 +3008,35 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>104025367</v>
+        <v>104025260</v>
       </c>
       <c r="B22" t="n">
-        <v>73693</v>
+        <v>90653</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3005,25 +3045,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3033,10 +3073,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>564434.643980975</v>
+        <v>564406.4858499069</v>
       </c>
       <c r="R22" t="n">
-        <v>7014725.134782875</v>
+        <v>7014734.483273009</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3068,7 +3108,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3078,7 +3118,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3109,10 +3149,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>104025369</v>
+        <v>104025367</v>
       </c>
       <c r="B23" t="n">
-        <v>96334</v>
+        <v>73693</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3121,25 +3161,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3149,10 +3189,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>564388.6566253824</v>
+        <v>564434.643980975</v>
       </c>
       <c r="R23" t="n">
-        <v>7014791.343799144</v>
+        <v>7014725.134782875</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3184,7 +3224,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3194,7 +3234,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3462,10 +3502,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>104025368</v>
+        <v>104025365</v>
       </c>
       <c r="B26" t="n">
-        <v>78569</v>
+        <v>77756</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3474,25 +3514,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3502,10 +3542,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>564404.7290194675</v>
+        <v>564389.6853632822</v>
       </c>
       <c r="R26" t="n">
-        <v>7014799.77459014</v>
+        <v>7014807.583181476</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3537,7 +3577,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3547,7 +3587,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3583,10 +3623,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>104025366</v>
+        <v>104025373</v>
       </c>
       <c r="B27" t="n">
-        <v>78596</v>
+        <v>78569</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3595,25 +3635,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3623,10 +3663,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>564386.5834773997</v>
+        <v>564352.6439708219</v>
       </c>
       <c r="R27" t="n">
-        <v>7014827.344051048</v>
+        <v>7014809.996464551</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3658,7 +3698,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3668,7 +3708,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3682,7 +3722,7 @@
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3697,1191 +3737,6 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>104025353</v>
-      </c>
-      <c r="B28" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Storberget-Storbergetjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>564358.7004139413</v>
-      </c>
-      <c r="R28" t="n">
-        <v>7014710.100289446</v>
-      </c>
-      <c r="S28" t="n">
-        <v>10</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AD28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>104025327</v>
-      </c>
-      <c r="B29" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Storberget-Storbergetjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q29" t="n">
-        <v>564457.3940783725</v>
-      </c>
-      <c r="R29" t="n">
-        <v>7014985.987806616</v>
-      </c>
-      <c r="S29" t="n">
-        <v>10</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>12:39</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>12:39</t>
-        </is>
-      </c>
-      <c r="AD29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>104025279</v>
-      </c>
-      <c r="B30" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Storberget-Storbergetjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>564469.776387642</v>
-      </c>
-      <c r="R30" t="n">
-        <v>7014953.349214448</v>
-      </c>
-      <c r="S30" t="n">
-        <v>10</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Sälglåga</t>
-        </is>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>104025356</v>
-      </c>
-      <c r="B31" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Storberget-Storbergetjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>564388.8793681564</v>
-      </c>
-      <c r="R31" t="n">
-        <v>7014712.505632785</v>
-      </c>
-      <c r="S31" t="n">
-        <v>10</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>10:47</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>10:47</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>104025365</v>
-      </c>
-      <c r="B32" t="n">
-        <v>77756</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>6459</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Barkkornlav</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Lopadium disciforme</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Flot.) Kullh.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Storberget-Storbergetjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>564389.6853632822</v>
-      </c>
-      <c r="R32" t="n">
-        <v>7014807.583181476</v>
-      </c>
-      <c r="S32" t="n">
-        <v>10</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>104025341</v>
-      </c>
-      <c r="B33" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Storberget-Storbergetjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>564454.0116622819</v>
-      </c>
-      <c r="R33" t="n">
-        <v>7014952.1326515</v>
-      </c>
-      <c r="S33" t="n">
-        <v>10</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AD33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>104025373</v>
-      </c>
-      <c r="B34" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Storberget-Storbergetjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>564352.6439708219</v>
-      </c>
-      <c r="R34" t="n">
-        <v>7014809.996464551</v>
-      </c>
-      <c r="S34" t="n">
-        <v>10</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
-      <c r="AD34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Asp</t>
-        </is>
-      </c>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>104025260</v>
-      </c>
-      <c r="B35" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Storberget-Storbergetjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>564406.4858499069</v>
-      </c>
-      <c r="R35" t="n">
-        <v>7014734.483273009</v>
-      </c>
-      <c r="S35" t="n">
-        <v>10</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>104025371</v>
-      </c>
-      <c r="B36" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Storberget-Storbergetjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>564350.8041544867</v>
-      </c>
-      <c r="R36" t="n">
-        <v>7014811.761785488</v>
-      </c>
-      <c r="S36" t="n">
-        <v>10</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>104025370</v>
-      </c>
-      <c r="B37" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Storberget-Storbergetjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>564373.5139542988</v>
-      </c>
-      <c r="R37" t="n">
-        <v>7014804.106251282</v>
-      </c>
-      <c r="S37" t="n">
-        <v>10</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>

--- a/artfynd/A 13483-2022 artfynd.xlsx
+++ b/artfynd/A 13483-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102897599</v>
+        <v>104025349</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storberget, Jmt</t>
+          <t>Storberget-Storbergetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564364.779983037</v>
+        <v>564494</v>
       </c>
       <c r="R2" t="n">
-        <v>7014721.935669066</v>
+        <v>7014946</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +770,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104025258</v>
+        <v>102897605</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,37 +797,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storberget-Storbergetjärnen, Jmt</t>
+          <t>Storberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564479.9584519536</v>
+        <v>564406</v>
       </c>
       <c r="R3" t="n">
-        <v>7014940.488491452</v>
+        <v>7014735</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:41</t>
+          <t>2022-08-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:41</t>
+          <t>2022-08-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,40 +867,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Asp</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104025368</v>
+        <v>104025260</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,21 +894,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564404.7290194675</v>
+        <v>564407</v>
       </c>
       <c r="R4" t="n">
-        <v>7014799.77459014</v>
+        <v>7014735</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +953,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +963,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,11 +974,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1029,15 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104025327</v>
+        <v>104025362</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1045,21 +1005,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1069,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564457.3940783725</v>
+        <v>564414</v>
       </c>
       <c r="R5" t="n">
-        <v>7014985.987806616</v>
+        <v>7014788</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,7 +1064,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1074,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,6 +1085,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1145,53 +1110,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102897582</v>
+        <v>104025367</v>
       </c>
       <c r="B6" t="n">
-        <v>77756</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6459</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storberget, Jmt</t>
+          <t>Storberget-Storbergetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564388.8104621168</v>
+        <v>564435</v>
       </c>
       <c r="R6" t="n">
-        <v>7014806.214124686</v>
+        <v>7014725</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,22 +1175,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,58 +1201,52 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104025312</v>
+        <v>104025364</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1302,10 +1256,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564509.341645895</v>
+        <v>564419</v>
       </c>
       <c r="R7" t="n">
-        <v>7014914.947627926</v>
+        <v>7014787</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,7 +1291,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1347,7 +1301,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,15 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104025371</v>
+        <v>104025258</v>
       </c>
       <c r="B8" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,21 +1343,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1418,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564350.8041544867</v>
+        <v>564480</v>
       </c>
       <c r="R8" t="n">
-        <v>7014811.761785488</v>
+        <v>7014941</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1463,7 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,6 +1423,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1494,15 +1448,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>102897585</v>
+        <v>102897578</v>
       </c>
       <c r="B9" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564350.8401479318</v>
+        <v>564469</v>
       </c>
       <c r="R9" t="n">
-        <v>7014809.960421473</v>
+        <v>7014954</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1567,21 +1516,11 @@
           <t>2022-08-15</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-08-15</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1593,7 +1532,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälglåga</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1611,15 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104025349</v>
+        <v>104025370</v>
       </c>
       <c r="B10" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1627,21 +1561,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1651,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564493.820275197</v>
+        <v>564374</v>
       </c>
       <c r="R10" t="n">
-        <v>7014946.622608646</v>
+        <v>7014803</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,7 +1620,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1696,7 +1630,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,6 +1641,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1727,53 +1666,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104025366</v>
+        <v>102897585</v>
       </c>
       <c r="B11" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Storberget-Storbergetjärnen, Jmt</t>
+          <t>Storberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564386.5834773997</v>
+        <v>564351</v>
       </c>
       <c r="R11" t="n">
-        <v>7014827.344051048</v>
+        <v>7014810</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1797,22 +1731,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:29</t>
+          <t>2022-08-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>10:29</t>
+          <t>2022-08-15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1826,37 +1750,28 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104025364</v>
+        <v>104025361</v>
       </c>
       <c r="B12" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,21 +1779,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1888,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564418.9789276946</v>
+        <v>564370</v>
       </c>
       <c r="R12" t="n">
-        <v>7014786.543879118</v>
+        <v>7014770</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1923,7 +1838,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1933,7 +1848,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1944,6 +1859,11 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1964,15 +1884,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104025279</v>
+        <v>102897594</v>
       </c>
       <c r="B13" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2000,17 +1915,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Storberget-Storbergetjärnen, Jmt</t>
+          <t>Storberget, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564469.776387642</v>
+        <v>564404</v>
       </c>
       <c r="R13" t="n">
-        <v>7014953.349214448</v>
+        <v>7014800</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2034,22 +1949,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:38</t>
+          <t>2022-08-15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:38</t>
+          <t>2022-08-15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2063,37 +1968,28 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Sälglåga</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104025370</v>
+        <v>104025358</v>
       </c>
       <c r="B14" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2125,10 +2021,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564373.5139542988</v>
+        <v>564358</v>
       </c>
       <c r="R14" t="n">
-        <v>7014804.106251282</v>
+        <v>7014717</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2160,7 +2056,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2170,7 +2066,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2206,50 +2102,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104025369</v>
+        <v>104025355</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Storberget-Storbergetjärnen, Jmt</t>
+          <t>Storberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>564388.6566253824</v>
+        <v>564345</v>
       </c>
       <c r="R15" t="n">
-        <v>7014791.343799144</v>
+        <v>7014735</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2281,7 +2172,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2291,7 +2182,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2322,53 +2213,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104025341</v>
+        <v>102897603</v>
       </c>
       <c r="B16" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Storberget-Storbergetjärnen, Jmt</t>
+          <t>Storberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564454.0116622819</v>
+        <v>564388</v>
       </c>
       <c r="R16" t="n">
-        <v>7014952.1326515</v>
+        <v>7014712</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2392,22 +2278,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:38</t>
+          <t>2022-08-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:38</t>
+          <t>2022-08-15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2418,35 +2294,31 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104025361</v>
+        <v>104025279</v>
       </c>
       <c r="B17" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,10 +2350,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564370.1304199966</v>
+        <v>564470</v>
       </c>
       <c r="R17" t="n">
-        <v>7014770.24930511</v>
+        <v>7014954</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2513,7 +2385,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2523,7 +2395,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2537,7 +2409,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Sälglåga</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2559,15 +2431,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104025363</v>
+        <v>104025356</v>
       </c>
       <c r="B18" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2575,21 +2442,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2599,10 +2466,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564418.9789276946</v>
+        <v>564389</v>
       </c>
       <c r="R18" t="n">
-        <v>7014786.543879118</v>
+        <v>7014712</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2634,7 +2501,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2644,7 +2511,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2655,6 +2522,11 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2675,37 +2547,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>104025353</v>
+        <v>104025368</v>
       </c>
       <c r="B19" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2715,10 +2582,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>564358.7004139413</v>
+        <v>564405</v>
       </c>
       <c r="R19" t="n">
-        <v>7014710.100289446</v>
+        <v>7014800</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2750,7 +2617,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2760,7 +2627,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2771,6 +2638,11 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2791,15 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>104025358</v>
+        <v>104025373</v>
       </c>
       <c r="B20" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2831,10 +2698,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>564357.6634856508</v>
+        <v>564352</v>
       </c>
       <c r="R20" t="n">
-        <v>7014716.837585099</v>
+        <v>7014810</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2866,7 +2733,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2876,7 +2743,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2890,7 +2757,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2912,53 +2779,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>104025356</v>
+        <v>102897582</v>
       </c>
       <c r="B21" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79583</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Storberget-Storbergetjärnen, Jmt</t>
+          <t>Storberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>564388.8793681564</v>
+        <v>564389</v>
       </c>
       <c r="R21" t="n">
-        <v>7014712.505632785</v>
+        <v>7014806</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2982,22 +2844,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2022-08-15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2022-08-15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3011,37 +2863,28 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>104025260</v>
+        <v>104025365</v>
       </c>
       <c r="B22" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79583</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3049,21 +2892,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6459</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3073,10 +2916,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>564406.4858499069</v>
+        <v>564390</v>
       </c>
       <c r="R22" t="n">
-        <v>7014734.483273009</v>
+        <v>7014807</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3108,7 +2951,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3118,7 +2961,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3129,6 +2972,11 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3149,53 +2997,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>104025367</v>
+        <v>102897583</v>
       </c>
       <c r="B23" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Storberget-Storbergetjärnen, Jmt</t>
+          <t>Storberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>564434.643980975</v>
+        <v>564386</v>
       </c>
       <c r="R23" t="n">
-        <v>7014725.134782875</v>
+        <v>7014826</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3219,22 +3062,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>10:43</t>
+          <t>2022-08-15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>10:43</t>
+          <t>2022-08-15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3245,57 +3078,53 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>104025354</v>
+        <v>104025360</v>
       </c>
       <c r="B24" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3305,10 +3134,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>564364.7529822935</v>
+        <v>564352</v>
       </c>
       <c r="R24" t="n">
-        <v>7014723.286729028</v>
+        <v>7014728</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3340,7 +3169,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3350,7 +3179,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3361,6 +3190,11 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3381,37 +3215,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>104025362</v>
+        <v>104025366</v>
       </c>
       <c r="B25" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3421,10 +3250,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>564413.9913565284</v>
+        <v>564386</v>
       </c>
       <c r="R25" t="n">
-        <v>7014787.795694167</v>
+        <v>7014827</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3456,7 +3285,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3466,7 +3295,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3480,7 +3309,7 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3502,53 +3331,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>104025365</v>
+        <v>102897579</v>
       </c>
       <c r="B26" t="n">
-        <v>77756</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6459</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Storberget-Storbergetjärnen, Jmt</t>
+          <t>Storberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>564389.6853632822</v>
+        <v>564454</v>
       </c>
       <c r="R26" t="n">
-        <v>7014807.583181476</v>
+        <v>7014951</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3572,22 +3396,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>10:28</t>
+          <t>2022-08-15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>10:28</t>
+          <t>2022-08-15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3598,78 +3412,64 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>104025373</v>
+        <v>102897580</v>
       </c>
       <c r="B27" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Storberget-Storbergetjärnen, Jmt</t>
+          <t>Storberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>564352.6439708219</v>
+        <v>564458</v>
       </c>
       <c r="R27" t="n">
-        <v>7014809.996464551</v>
+        <v>7014985</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3693,22 +3493,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:05</t>
+          <t>2022-08-15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>10:05</t>
+          <t>2022-08-15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3719,24 +3509,1707 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Asp</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>104025312</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Storberget-Storbergetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>564509</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7014915</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
+      <c r="AX28" t="inlineStr">
         <is>
           <t>Via Johan Staaf</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr">
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>102897592</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Storberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>564389</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7014790</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2022-08-15</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2022-08-15</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>102897597</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Storberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>564358</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7014709</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2022-08-15</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2022-08-15</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>102897599</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Storberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>564365</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7014722</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2022-08-15</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2022-08-15</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>102897601</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Storberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>564343</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7014730</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2022-08-15</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2022-08-15</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>104025327</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Storberget-Storbergetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>564458</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7014986</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>104025341</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Storberget-Storbergetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>564454</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7014952</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>104025353</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Storberget-Storbergetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>564359</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7014710</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>104025354</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Storberget-Storbergetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>564365</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7014723</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>104025359</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Storberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>564343</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7014731</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>104025369</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Storberget-Storbergetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>564389</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7014791</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>102897595</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Storberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>564352</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7014705</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2022-08-15</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2022-08-15</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>104025352</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Storberget-Storbergetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>564353</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7014706</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>104025363</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Storberget-Storbergetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>564419</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7014787</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>102897593</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Storberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>564351</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7014811</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2022-08-15</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2022-08-15</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>104025371</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Storberget-Storbergetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>564351</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7014812</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>

--- a/artfynd/A 13483-2022 artfynd.xlsx
+++ b/artfynd/A 13483-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025349</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102897605</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,6 +1006,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025260</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,6 +1127,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025362</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1218,6 +1243,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025367</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1329,6 +1359,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025364</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1445,6 +1480,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025258</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1547,6 +1587,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102897578</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1663,6 +1708,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025370</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1765,6 +1815,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102897585</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1881,6 +1936,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025361</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1983,6 +2043,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102897594</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2099,6 +2164,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025358</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2210,6 +2280,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025355</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2312,6 +2387,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102897603</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2428,6 +2508,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025279</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2544,6 +2629,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025356</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2660,6 +2750,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025368</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2776,6 +2871,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025373</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2878,6 +2978,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102897582</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2994,6 +3099,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025365</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3096,6 +3206,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102897583</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3212,6 +3327,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025360</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3328,6 +3448,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025366</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3425,6 +3550,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102897579</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3522,6 +3652,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102897580</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3633,6 +3768,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025312</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3730,6 +3870,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102897592</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3827,6 +3972,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102897597</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3924,6 +4074,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102897599</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4021,6 +4176,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102897601</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4132,6 +4292,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025327</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4243,6 +4408,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025341</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4354,6 +4524,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025353</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4465,6 +4640,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025354</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4576,6 +4756,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025359</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4687,6 +4872,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025369</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4784,6 +4974,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102897595</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4895,6 +5090,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025352</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5006,6 +5206,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025363</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5103,6 +5308,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102897593</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5214,8 +5424,57 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025371</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>